--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_16-10-2025.xlsx
@@ -543,12 +543,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -780,12 +780,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1264,17 +1264,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£20.90</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.10</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.10</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
